--- a/relatorios/monitoramento_2026-07-17.xlsx
+++ b/relatorios/monitoramento_2026-07-17.xlsx
@@ -1,28 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gsilva11\Documents\RAG_DO_MINERu\relatorios\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A775266-DD90-4EE9-9E29-85D91FDFDFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumo" sheetId="1" r:id="rId1"/>
-    <sheet name="1 - Prazos Criticos" sheetId="2" r:id="rId2"/>
-    <sheet name="2 - Movimentacoes de Pessoal" sheetId="3" r:id="rId3"/>
-    <sheet name="3 - Nomes Monitorados" sheetId="4" r:id="rId4"/>
-    <sheet name="4 - Observacoes Executivas" sheetId="5" r:id="rId5"/>
-    <sheet name="5 - Expediente e Ponto Facultat" sheetId="6" r:id="rId6"/>
-    <sheet name="6 - Tribunal de Contas (IB)" sheetId="7" r:id="rId7"/>
-    <sheet name="7 - Poder Legislativo (II)" sheetId="8" r:id="rId8"/>
-    <sheet name="8 - Municipalidades e Pedido (I" sheetId="9" r:id="rId9"/>
+    <sheet name="Planilha2" sheetId="11" r:id="rId1"/>
+    <sheet name="Resumo" sheetId="1" r:id="rId2"/>
+    <sheet name="1 - Prazos Criticos" sheetId="2" r:id="rId3"/>
+    <sheet name="2 - Movimentacoes de Pessoal" sheetId="3" r:id="rId4"/>
+    <sheet name="3 - Nomes Monitorados" sheetId="4" r:id="rId5"/>
+    <sheet name="4 - Observacoes Executivas" sheetId="5" r:id="rId6"/>
+    <sheet name="5 - Expediente e Ponto Facultat" sheetId="6" r:id="rId7"/>
+    <sheet name="6 - Tribunal de Contas (IB)" sheetId="7" r:id="rId8"/>
+    <sheet name="7 - Poder Legislativo (II)" sheetId="8" r:id="rId9"/>
+    <sheet name="8 - Municipalidades e Pedido (I" sheetId="9" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="235">
   <si>
     <t>Monitoramento DOERJ (estruturado) - 2026-07-17</t>
   </si>
@@ -732,8 +752,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -814,13 +834,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -858,7 +886,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -892,6 +920,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -926,9 +955,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1101,100 +1131,319 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="40.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D753C78D-C079-4A85-97F2-B402AC46242B}">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>76</v>
+      </c>
+      <c r="B2">
+        <v>34</v>
+      </c>
+      <c r="C2">
+        <v>84</v>
+      </c>
+      <c r="D2">
+        <v>237</v>
+      </c>
+      <c r="E2">
+        <v>66</v>
+      </c>
+      <c r="F2">
+        <v>133</v>
+      </c>
+      <c r="G2">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>467</v>
+      </c>
+      <c r="I2">
+        <v>29</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>A2/8*1.5</f>
+        <v>14.25</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:J3" si="0">B2/8*1.5</f>
+        <v>6.375</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>15.75</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>44.4375</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>12.375</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>24.9375</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="0"/>
+        <v>6.5625</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>87.5625</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>5.4375</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>45</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>88</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>4</v>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f>A4*8</f>
+        <v>120</v>
       </c>
       <c r="B5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+        <f t="shared" ref="B5:J5" si="1">B4*8</f>
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>704</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11">
+        <v>120</v>
+      </c>
+      <c r="O11" t="str">
+        <f>M11&amp;" AS VARCHAR2("&amp;N11&amp;");"</f>
+        <v>Tipo do Ato AS VARCHAR2(120);</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N12">
+        <v>56</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" ref="O12:O20" si="2">M12&amp;" AS VARCHAR2("&amp;N12&amp;");"</f>
+        <v>Numero/Ano AS VARCHAR2(56);</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M13" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <v>128</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="2"/>
+        <v>Orgao AS VARCHAR2(128);</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+      <c r="N14">
+        <v>360</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="2"/>
+        <v>Pessoa AS VARCHAR2(360);</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15">
+        <v>104</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="2"/>
+        <v>Cargo AS VARCHAR2(104);</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>16</v>
+      </c>
+      <c r="N16">
+        <v>200</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="2"/>
+        <v>Processo AS VARCHAR2(200);</v>
+      </c>
+    </row>
+    <row r="17" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17">
+        <v>56</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="2"/>
+        <v>Vigencia AS VARCHAR2(56);</v>
+      </c>
+    </row>
+    <row r="18" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18">
+        <v>704</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="2"/>
+        <v>Resumo AS VARCHAR2(704);</v>
+      </c>
+    </row>
+    <row r="19" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>19</v>
+      </c>
+      <c r="N19">
+        <v>48</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="2"/>
+        <v>Caderno AS VARCHAR2(48);</v>
+      </c>
+    </row>
+    <row r="20" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M20" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20">
+        <v>8</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="2"/>
+        <v>Pagina AS VARCHAR2(8);</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -1206,7 +1455,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1238,110 +1487,100 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
         <v>25</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>41</v>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1350,9 +1589,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -1364,7 +1603,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1396,126 +1635,110 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H2" s="3" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>58</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>72</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1524,9 +1747,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -1538,7 +1761,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1570,64 +1793,126 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>81</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>84</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="H3" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1636,9 +1921,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -1650,7 +1935,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1682,728 +1967,64 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="C2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="F2" s="3" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2412,9 +2033,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -2426,7 +2047,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -2458,9 +2079,728 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>201</v>
+        <v>89</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2469,9 +2809,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -2483,7 +2823,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -2515,62 +2855,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2579,9 +2866,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -2593,7 +2880,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -2625,95 +2912,61 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>221</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>223</v>
+        <v>40</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>219</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>226</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>223</v>
+        <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J4" s="3" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2723,9 +2976,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="4" width="26.7109375" customWidth="1"/>
@@ -2737,7 +2990,7 @@
     <col min="10" max="10" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -2769,9 +3022,96 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
